--- a/storage/app/private/CLIENTES/MIGUEL_LUCHO/Bitacora_MIGUEL_LUCHO_JUNIO-2026.xlsx
+++ b/storage/app/private/CLIENTES/MIGUEL_LUCHO/Bitacora_MIGUEL_LUCHO_JUNIO-2026.xlsx
@@ -1,22 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\ComandosBitacora\storage\app\private\CLIENTES\MIGUEL_LUCHO\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492DC124-9C20-4334-83B8-7D18A11AF5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="1" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Facturas" sheetId="1" r:id="rId4"/>
-    <sheet name="Fichas" sheetId="2" r:id="rId5"/>
+    <sheet name="Facturas" sheetId="1" r:id="rId1"/>
+    <sheet name="Fichas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>Facturas De Miguel_lucho</t>
   </si>
@@ -61,57 +79,57 @@
   </si>
   <si>
     <t>MONTO</t>
+  </si>
+  <si>
+    <t>gamaliel</t>
+  </si>
+  <si>
+    <t>6/7/2026</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>patricia</t>
+  </si>
+  <si>
+    <t>6/1/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF548235"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF595959"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -175,34 +193,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="164" fillId="0" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="3" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -492,31 +519,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.846" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="43.561" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="45.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -533,7 +557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -547,10 +571,10 @@
         <v>9</v>
       </c>
       <c r="E5" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D6" s="8" t="s">
         <v>10</v>
       </c>
@@ -560,47 +584,33 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="66.555" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="45.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -617,16 +627,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="13">
+        <v>500</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -635,7 +653,7 @@
       <c r="D6" s="12"/>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -644,7 +662,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>4</v>
       </c>
@@ -653,16 +671,18 @@
       <c r="D8" s="12"/>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>5</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="7"/>
+      <c r="D9" s="13">
+        <v>100</v>
+      </c>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>6</v>
       </c>
@@ -671,27 +691,65 @@
       <c r="D10" s="12"/>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:5">
-      <c r="C11" s="8" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="13">
+        <v>1000</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="9">
-        <f>SUM(D5:D10)</f>
-        <v>0</v>
+      <c r="D16" s="9">
+        <f>SUM(D5:D15)</f>
+        <v>1600</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>